--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orti urbani (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Orti urbani (1).xlsx
@@ -723,7 +723,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
 Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
@@ -1163,16 +1163,16 @@
     </r>
   </si>
   <si>
-    <t>-</t>
+    <t>n/a</t>
   </si>
   <si>
     <t>Vai alla graduatoria</t>
   </si>
   <si>
-    <t>Avviso di pagamento</t>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
   </si>
   <si>
-    <t>Vedi Avviso</t>
+    <t>-</t>
   </si>
   <si>
     <r>
@@ -1188,6 +1188,12 @@
     </r>
   </si>
   <si>
+    <t>**📎 **Allegato Premium: &lt;testo integrale del bando&gt;</t>
+  </si>
+  <si>
+    <t>**📎 **Allegato Premium: &lt;regolamento&gt;</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1199,12 +1205,6 @@
       <t xml:space="preserve">
 File allegato al messaggio</t>
     </r>
-  </si>
-  <si>
-    <t>&lt;testo integrale del bando&gt;</t>
-  </si>
-  <si>
-    <t>&lt;regolamento&gt;</t>
   </si>
   <si>
     <r>
@@ -1257,7 +1257,7 @@
     <t>Quando l’ente pubblica pubblica la graduatoria per l’assegnazione di orti urbani.</t>
   </si>
   <si>
-    <t>Quando, a seguito dell’assegnazione,  l’ente deve comunicare agli assegnatari i dettagli sulla assegnazione del lotto.</t>
+    <t>Quando, a seguito dell’assegnazione, l’ente deve comunicare agli assegnatari i dettagli sulla assegnazione del lotto.</t>
   </si>
   <si>
     <t>Quando è necessario effettuare il pagamento del canone annuale.</t>
@@ -2078,25 +2078,25 @@
         <v>99</v>
       </c>
       <c r="F6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="I6" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>97</v>
-      </c>
       <c r="J6" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L6" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2104,13 +2104,13 @@
         <v>101</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>61</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>61</v>
+        <v>103</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>61</v>
@@ -2139,40 +2139,40 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
